--- a/outputs/lpg_weight_robustness.xlsx
+++ b/outputs/lpg_weight_robustness.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -432,8 +432,8 @@
     <col width="17" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="44" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,6 +505,118 @@
       <c r="N1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LPG</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C2" t="n">
+        <v>54</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-15.1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-17.8</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>WEIGHT-ROBUST</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>position TRIM/SHORT across all 3 weight sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BWLP</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="C3" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="D3" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-21.9</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-18.8</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>14</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-24.4</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>WEIGHT-ROBUST</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>position TRIM/SHORT across all 3 weight sets</t>
         </is>
       </c>
     </row>

--- a/outputs/lpg_weight_robustness.xlsx
+++ b/outputs/lpg_weight_robustness.xlsx
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36</v>
+        <v>40.05</v>
       </c>
       <c r="C2" t="n">
         <v>54</v>
@@ -524,7 +524,7 @@
         <v>30.55</v>
       </c>
       <c r="E2" t="n">
-        <v>-15.1</v>
+        <v>-23.7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
         <v>31.75</v>
       </c>
       <c r="H2" t="n">
-        <v>-11.8</v>
+        <v>-20.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
         <v>29.58</v>
       </c>
       <c r="K2" t="n">
-        <v>-17.8</v>
+        <v>-26.1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.52</v>
+        <v>19.45</v>
       </c>
       <c r="C3" t="n">
         <v>17.52</v>
@@ -580,7 +580,7 @@
         <v>14.46</v>
       </c>
       <c r="E3" t="n">
-        <v>-21.9</v>
+        <v>-25.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         <v>15.04</v>
       </c>
       <c r="H3" t="n">
-        <v>-18.8</v>
+        <v>-22.7</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>-24.4</v>
+        <v>-28</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>

--- a/outputs/lpg_weight_robustness.xlsx
+++ b/outputs/lpg_weight_robustness.xlsx
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>40.05</v>
+        <v>40.14</v>
       </c>
       <c r="C2" t="n">
         <v>54</v>
@@ -524,7 +524,7 @@
         <v>30.55</v>
       </c>
       <c r="E2" t="n">
-        <v>-23.7</v>
+        <v>-23.9</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
         <v>31.75</v>
       </c>
       <c r="H2" t="n">
-        <v>-20.7</v>
+        <v>-20.9</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
         <v>29.58</v>
       </c>
       <c r="K2" t="n">
-        <v>-26.1</v>
+        <v>-26.3</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.45</v>
+        <v>20.1</v>
       </c>
       <c r="C3" t="n">
         <v>17.52</v>
@@ -580,7 +580,7 @@
         <v>14.46</v>
       </c>
       <c r="E3" t="n">
-        <v>-25.6</v>
+        <v>-28</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         <v>15.04</v>
       </c>
       <c r="H3" t="n">
-        <v>-22.7</v>
+        <v>-25.2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>-28</v>
+        <v>-30.3</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>

--- a/outputs/lpg_weight_robustness.xlsx
+++ b/outputs/lpg_weight_robustness.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>40.14</v>
+        <v>41.63</v>
       </c>
       <c r="C2" t="n">
         <v>54</v>
@@ -524,7 +524,7 @@
         <v>30.55</v>
       </c>
       <c r="E2" t="n">
-        <v>-23.9</v>
+        <v>-26.6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
         <v>31.75</v>
       </c>
       <c r="H2" t="n">
-        <v>-20.9</v>
+        <v>-23.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
         <v>29.58</v>
       </c>
       <c r="K2" t="n">
-        <v>-26.3</v>
+        <v>-29</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.1</v>
+        <v>21.1556</v>
       </c>
       <c r="C3" t="n">
         <v>17.52</v>
@@ -580,7 +580,7 @@
         <v>14.46</v>
       </c>
       <c r="E3" t="n">
-        <v>-28</v>
+        <v>-31.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         <v>15.04</v>
       </c>
       <c r="H3" t="n">
-        <v>-25.2</v>
+        <v>-28.9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>-30.3</v>
+        <v>-33.8</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>

--- a/outputs/lpg_weight_robustness.xlsx
+++ b/outputs/lpg_weight_robustness.xlsx
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41.63</v>
+        <v>41.03</v>
       </c>
       <c r="C2" t="n">
         <v>54</v>
@@ -524,7 +524,7 @@
         <v>30.55</v>
       </c>
       <c r="E2" t="n">
-        <v>-26.6</v>
+        <v>-25.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
         <v>31.75</v>
       </c>
       <c r="H2" t="n">
-        <v>-23.7</v>
+        <v>-22.6</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
         <v>29.58</v>
       </c>
       <c r="K2" t="n">
-        <v>-29</v>
+        <v>-27.9</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.1556</v>
+        <v>20.3488</v>
       </c>
       <c r="C3" t="n">
         <v>17.52</v>
@@ -580,7 +580,7 @@
         <v>14.46</v>
       </c>
       <c r="E3" t="n">
-        <v>-31.6</v>
+        <v>-28.9</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         <v>15.04</v>
       </c>
       <c r="H3" t="n">
-        <v>-28.9</v>
+        <v>-26.1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>-33.8</v>
+        <v>-31.2</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>

--- a/outputs/lpg_weight_robustness.xlsx
+++ b/outputs/lpg_weight_robustness.xlsx
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41.03</v>
+        <v>43.09</v>
       </c>
       <c r="C2" t="n">
         <v>54</v>
@@ -524,7 +524,7 @@
         <v>30.55</v>
       </c>
       <c r="E2" t="n">
-        <v>-25.5</v>
+        <v>-29.1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
         <v>31.75</v>
       </c>
       <c r="H2" t="n">
-        <v>-22.6</v>
+        <v>-26.3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
         <v>29.58</v>
       </c>
       <c r="K2" t="n">
-        <v>-27.9</v>
+        <v>-31.4</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.3488</v>
+        <v>21.1029</v>
       </c>
       <c r="C3" t="n">
         <v>17.52</v>
@@ -580,7 +580,7 @@
         <v>14.46</v>
       </c>
       <c r="E3" t="n">
-        <v>-28.9</v>
+        <v>-31.5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         <v>15.04</v>
       </c>
       <c r="H3" t="n">
-        <v>-26.1</v>
+        <v>-28.7</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>-31.2</v>
+        <v>-33.7</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>

--- a/outputs/lpg_weight_robustness.xlsx
+++ b/outputs/lpg_weight_robustness.xlsx
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43.09</v>
+        <v>45.32</v>
       </c>
       <c r="C2" t="n">
         <v>54</v>
@@ -524,7 +524,7 @@
         <v>30.55</v>
       </c>
       <c r="E2" t="n">
-        <v>-29.1</v>
+        <v>-32.6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
         <v>31.75</v>
       </c>
       <c r="H2" t="n">
-        <v>-26.3</v>
+        <v>-30</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
         <v>29.58</v>
       </c>
       <c r="K2" t="n">
-        <v>-31.4</v>
+        <v>-34.7</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.1029</v>
+        <v>21.9952</v>
       </c>
       <c r="C3" t="n">
         <v>17.52</v>
@@ -580,7 +580,7 @@
         <v>14.46</v>
       </c>
       <c r="E3" t="n">
-        <v>-31.5</v>
+        <v>-34.2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         <v>15.04</v>
       </c>
       <c r="H3" t="n">
-        <v>-28.7</v>
+        <v>-31.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>-33.7</v>
+        <v>-36.3</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>

--- a/outputs/lpg_weight_robustness.xlsx
+++ b/outputs/lpg_weight_robustness.xlsx
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45.32</v>
+        <v>46.54</v>
       </c>
       <c r="C2" t="n">
         <v>54</v>
@@ -524,7 +524,7 @@
         <v>30.55</v>
       </c>
       <c r="E2" t="n">
-        <v>-32.6</v>
+        <v>-34.4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
         <v>31.75</v>
       </c>
       <c r="H2" t="n">
-        <v>-30</v>
+        <v>-31.8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
         <v>29.58</v>
       </c>
       <c r="K2" t="n">
-        <v>-34.7</v>
+        <v>-36.4</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.9952</v>
+        <v>22.7028</v>
       </c>
       <c r="C3" t="n">
         <v>17.52</v>
@@ -580,7 +580,7 @@
         <v>14.46</v>
       </c>
       <c r="E3" t="n">
-        <v>-34.2</v>
+        <v>-36.3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         <v>15.04</v>
       </c>
       <c r="H3" t="n">
-        <v>-31.6</v>
+        <v>-33.8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>-36.3</v>
+        <v>-38.3</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>

--- a/outputs/lpg_weight_robustness.xlsx
+++ b/outputs/lpg_weight_robustness.xlsx
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46.54</v>
+        <v>45.76</v>
       </c>
       <c r="C2" t="n">
         <v>54</v>
@@ -524,7 +524,7 @@
         <v>30.55</v>
       </c>
       <c r="E2" t="n">
-        <v>-34.4</v>
+        <v>-33.2</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
         <v>31.75</v>
       </c>
       <c r="H2" t="n">
-        <v>-31.8</v>
+        <v>-30.6</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
         <v>29.58</v>
       </c>
       <c r="K2" t="n">
-        <v>-36.4</v>
+        <v>-35.4</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22.7028</v>
+        <v>21.6026</v>
       </c>
       <c r="C3" t="n">
         <v>17.52</v>
@@ -580,7 +580,7 @@
         <v>14.46</v>
       </c>
       <c r="E3" t="n">
-        <v>-36.3</v>
+        <v>-33</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         <v>15.04</v>
       </c>
       <c r="H3" t="n">
-        <v>-33.8</v>
+        <v>-30.4</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>-38.3</v>
+        <v>-35.2</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>

--- a/outputs/lpg_weight_robustness.xlsx
+++ b/outputs/lpg_weight_robustness.xlsx
@@ -521,10 +521,10 @@
         <v>54</v>
       </c>
       <c r="D2" t="n">
-        <v>30.55</v>
+        <v>31.82</v>
       </c>
       <c r="E2" t="n">
-        <v>-33.2</v>
+        <v>-30.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>31.75</v>
+        <v>32.84</v>
       </c>
       <c r="H2" t="n">
-        <v>-30.6</v>
+        <v>-28.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>29.58</v>
+        <v>31</v>
       </c>
       <c r="K2" t="n">
-        <v>-35.4</v>
+        <v>-32.3</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>

--- a/outputs/lpg_weight_robustness.xlsx
+++ b/outputs/lpg_weight_robustness.xlsx
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45.76</v>
+        <v>47.37</v>
       </c>
       <c r="C2" t="n">
         <v>54</v>
@@ -524,7 +524,7 @@
         <v>31.82</v>
       </c>
       <c r="E2" t="n">
-        <v>-30.5</v>
+        <v>-32.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
         <v>32.84</v>
       </c>
       <c r="H2" t="n">
-        <v>-28.2</v>
+        <v>-30.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
         <v>31</v>
       </c>
       <c r="K2" t="n">
-        <v>-32.3</v>
+        <v>-34.6</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.6026</v>
+        <v>22.7519</v>
       </c>
       <c r="C3" t="n">
         <v>17.52</v>
@@ -580,7 +580,7 @@
         <v>14.46</v>
       </c>
       <c r="E3" t="n">
-        <v>-33</v>
+        <v>-36.4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         <v>15.04</v>
       </c>
       <c r="H3" t="n">
-        <v>-30.4</v>
+        <v>-33.9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>-35.2</v>
+        <v>-38.5</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>

--- a/outputs/lpg_weight_robustness.xlsx
+++ b/outputs/lpg_weight_robustness.xlsx
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47.37</v>
+        <v>50.79</v>
       </c>
       <c r="C2" t="n">
         <v>54</v>
@@ -524,7 +524,7 @@
         <v>31.82</v>
       </c>
       <c r="E2" t="n">
-        <v>-32.8</v>
+        <v>-37.3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
         <v>32.84</v>
       </c>
       <c r="H2" t="n">
-        <v>-30.7</v>
+        <v>-35.3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
         <v>31</v>
       </c>
       <c r="K2" t="n">
-        <v>-34.6</v>
+        <v>-39</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22.7519</v>
+        <v>25.0838</v>
       </c>
       <c r="C3" t="n">
         <v>17.52</v>
@@ -580,7 +580,7 @@
         <v>14.46</v>
       </c>
       <c r="E3" t="n">
-        <v>-36.4</v>
+        <v>-42.3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         <v>15.04</v>
       </c>
       <c r="H3" t="n">
-        <v>-33.9</v>
+        <v>-40</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>-38.5</v>
+        <v>-44.2</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>

--- a/outputs/lpg_weight_robustness.xlsx
+++ b/outputs/lpg_weight_robustness.xlsx
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50.79</v>
+        <v>49.78</v>
       </c>
       <c r="C2" t="n">
         <v>54</v>
@@ -524,7 +524,7 @@
         <v>31.82</v>
       </c>
       <c r="E2" t="n">
-        <v>-37.3</v>
+        <v>-36.1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
         <v>32.84</v>
       </c>
       <c r="H2" t="n">
-        <v>-35.3</v>
+        <v>-34</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
         <v>31</v>
       </c>
       <c r="K2" t="n">
-        <v>-39</v>
+        <v>-37.7</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25.0838</v>
+        <v>24.0493</v>
       </c>
       <c r="C3" t="n">
         <v>17.52</v>
@@ -580,7 +580,7 @@
         <v>14.46</v>
       </c>
       <c r="E3" t="n">
-        <v>-42.3</v>
+        <v>-39.9</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         <v>15.04</v>
       </c>
       <c r="H3" t="n">
-        <v>-40</v>
+        <v>-37.5</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>-44.2</v>
+        <v>-41.8</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>

--- a/outputs/lpg_weight_robustness.xlsx
+++ b/outputs/lpg_weight_robustness.xlsx
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24.0493</v>
+        <v>24.0503</v>
       </c>
       <c r="C3" t="n">
         <v>17.52</v>

--- a/outputs/lpg_weight_robustness.xlsx
+++ b/outputs/lpg_weight_robustness.xlsx
@@ -577,10 +577,10 @@
         <v>17.52</v>
       </c>
       <c r="D3" t="n">
-        <v>14.46</v>
+        <v>14.52</v>
       </c>
       <c r="E3" t="n">
-        <v>-39.9</v>
+        <v>-39.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>15.04</v>
+        <v>15.09</v>
       </c>
       <c r="H3" t="n">
-        <v>-37.5</v>
+        <v>-37.3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>14</v>
+        <v>14.06</v>
       </c>
       <c r="K3" t="n">
-        <v>-41.8</v>
+        <v>-41.5</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
